--- a/Agile_Sheets/Agile_Template_v0.1.xlsx
+++ b/Agile_Sheets/Agile_Template_v0.1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Infosys Internship\infosys_Project\Agile_Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542FAC93-0E5A-47C7-86F7-DE7F1E6A98C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4519637-EF3A-4933-B3D1-43E7CE504534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,9 +183,6 @@
     <t>Sprint 10 (22/03/26)</t>
   </si>
   <si>
-    <t>I want to refine and update the frontend and backend after integration so that the complete KYC verification system becomes functional and works accurately</t>
-  </si>
-  <si>
     <t>Integrated KYC pipeline, GNN models, OCR extraction, Secure API (Backend), Verification page (Frontend) , DB</t>
   </si>
   <si>
@@ -1280,6 +1277,9 @@
   </si>
   <si>
     <t>Added Hardhat test suite for smart contract before mainnet deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I want to refine and update the frontend and backend after integration so that the complete KYC verification system becomes functional and works accurately </t>
   </si>
 </sst>
 </file>
@@ -1618,16 +1618,16 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2128,13 +2128,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>51</v>
+        <v>415</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>14</v>
@@ -2145,25 +2145,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>15</v>
@@ -2171,25 +2171,25 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>15</v>
@@ -2197,22 +2197,22 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -2223,25 +2223,25 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>15</v>
@@ -2249,22 +2249,22 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -7217,101 +7217,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="33"/>
+      <c r="A1" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="36"/>
     </row>
     <row r="2" spans="1:23" ht="42" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>82</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="K2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="P2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="Q2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="R2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="S2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="T2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="U2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="V2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15.75" customHeight="1">
@@ -7370,56 +7370,56 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1">
-      <c r="A4" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="36"/>
+      <c r="A4" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="33"/>
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>103</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>104</v>
       </c>
       <c r="I5" s="14">
         <v>2</v>
@@ -7472,25 +7472,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="D6" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>107</v>
-      </c>
       <c r="H6" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I6" s="17">
         <v>4</v>
@@ -7543,25 +7543,25 @@
         <v>10</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>109</v>
-      </c>
       <c r="D7" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>102</v>
-      </c>
       <c r="G7" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I7" s="14">
         <v>3</v>
@@ -7614,25 +7614,25 @@
         <v>10</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>111</v>
-      </c>
       <c r="D8" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>102</v>
-      </c>
       <c r="G8" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" s="17">
         <v>3</v>
@@ -7685,25 +7685,25 @@
         <v>10</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="D9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>114</v>
-      </c>
       <c r="H9" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I9" s="14">
         <v>4</v>
@@ -7752,56 +7752,56 @@
       </c>
     </row>
     <row r="10" spans="1:23" ht="18" customHeight="1">
-      <c r="A10" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="36"/>
+      <c r="A10" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="33"/>
     </row>
     <row r="11" spans="1:23" ht="21.75" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="E11" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>120</v>
-      </c>
       <c r="H11" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I11" s="14">
         <v>3</v>
@@ -7854,25 +7854,25 @@
         <v>18</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>122</v>
-      </c>
       <c r="D12" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>120</v>
-      </c>
       <c r="H12" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I12" s="17">
         <v>4</v>
@@ -7925,25 +7925,25 @@
         <v>18</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="D13" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>125</v>
-      </c>
       <c r="H13" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I13" s="14">
         <v>4</v>
@@ -7996,25 +7996,25 @@
         <v>18</v>
       </c>
       <c r="B14" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="D14" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>128</v>
-      </c>
       <c r="H14" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I14" s="17">
         <v>3</v>
@@ -8063,56 +8063,56 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="18" customHeight="1">
-      <c r="A15" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="36"/>
+      <c r="A15" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="33"/>
     </row>
     <row r="16" spans="1:23" ht="21.75" customHeight="1">
       <c r="A16" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>132</v>
-      </c>
       <c r="H16" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I16" s="14">
         <v>3</v>
@@ -8165,25 +8165,25 @@
         <v>10</v>
       </c>
       <c r="B17" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>134</v>
-      </c>
       <c r="D17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I17" s="17">
         <v>3</v>
@@ -8236,25 +8236,25 @@
         <v>10</v>
       </c>
       <c r="B18" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>136</v>
-      </c>
       <c r="D18" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I18" s="14">
         <v>3</v>
@@ -8307,25 +8307,25 @@
         <v>10</v>
       </c>
       <c r="B19" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="D19" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>139</v>
-      </c>
       <c r="H19" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I19" s="17">
         <v>4</v>
@@ -8378,25 +8378,25 @@
         <v>10</v>
       </c>
       <c r="B20" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>141</v>
-      </c>
       <c r="D20" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I20" s="14">
         <v>2</v>
@@ -8445,56 +8445,56 @@
       </c>
     </row>
     <row r="21" spans="1:23" ht="18" customHeight="1">
-      <c r="A21" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="36"/>
+      <c r="A21" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="33"/>
     </row>
     <row r="22" spans="1:23" ht="21.75" customHeight="1">
       <c r="A22" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="D22" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>145</v>
-      </c>
       <c r="E22" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -8547,25 +8547,25 @@
         <v>26</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>148</v>
-      </c>
       <c r="D23" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I23" s="17">
         <v>3</v>
@@ -8618,25 +8618,25 @@
         <v>26</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="D24" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I24" s="14">
         <v>4</v>
@@ -8689,25 +8689,25 @@
         <v>26</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="C25" s="18" t="s">
-        <v>154</v>
-      </c>
       <c r="D25" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>29</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I25" s="17">
         <v>4</v>
@@ -8760,25 +8760,25 @@
         <v>26</v>
       </c>
       <c r="B26" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="D26" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I26" s="14">
         <v>1</v>
@@ -8827,56 +8827,56 @@
       </c>
     </row>
     <row r="27" spans="1:23" ht="18" customHeight="1">
-      <c r="A27" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="36"/>
+      <c r="A27" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="33"/>
     </row>
     <row r="28" spans="1:23" ht="21.75" customHeight="1">
       <c r="A28" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="E28" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="G28" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
@@ -8926,28 +8926,28 @@
     </row>
     <row r="29" spans="1:23" ht="21.75" customHeight="1">
       <c r="A29" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="D29" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>166</v>
-      </c>
       <c r="G29" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I29" s="17">
         <v>3</v>
@@ -8997,28 +8997,28 @@
     </row>
     <row r="30" spans="1:23" ht="21.75" customHeight="1">
       <c r="A30" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>170</v>
-      </c>
       <c r="G30" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -9068,28 +9068,28 @@
     </row>
     <row r="31" spans="1:23" ht="21.75" customHeight="1">
       <c r="A31" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B31" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>172</v>
-      </c>
       <c r="D31" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="E31" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>162</v>
-      </c>
       <c r="G31" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I31" s="17">
         <v>3</v>
@@ -9139,28 +9139,28 @@
     </row>
     <row r="32" spans="1:23" ht="21.75" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B32" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>174</v>
-      </c>
       <c r="D32" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I32" s="14">
         <v>2</v>
@@ -9209,56 +9209,56 @@
       </c>
     </row>
     <row r="33" spans="1:23" ht="18" customHeight="1">
-      <c r="A33" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35"/>
-      <c r="U33" s="35"/>
-      <c r="V33" s="35"/>
-      <c r="W33" s="36"/>
+      <c r="A33" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="33"/>
     </row>
     <row r="34" spans="1:23" ht="21.75" customHeight="1">
       <c r="A34" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B34" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="E34" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I34" s="14">
         <v>6</v>
@@ -9311,25 +9311,25 @@
         <v>10</v>
       </c>
       <c r="B35" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="18" t="s">
-        <v>180</v>
-      </c>
       <c r="D35" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I35" s="17">
         <v>3</v>
@@ -9382,25 +9382,25 @@
         <v>10</v>
       </c>
       <c r="B36" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>182</v>
-      </c>
       <c r="D36" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I36" s="14">
         <v>3</v>
@@ -9453,25 +9453,25 @@
         <v>10</v>
       </c>
       <c r="B37" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="18" t="s">
-        <v>184</v>
-      </c>
       <c r="D37" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I37" s="17">
         <v>2</v>
@@ -9524,25 +9524,25 @@
         <v>10</v>
       </c>
       <c r="B38" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C38" s="15" t="s">
-        <v>186</v>
-      </c>
       <c r="D38" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I38" s="14">
         <v>3</v>
@@ -9591,56 +9591,56 @@
       </c>
     </row>
     <row r="39" spans="1:23" ht="18" customHeight="1">
-      <c r="A39" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="35"/>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="36"/>
+      <c r="A39" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="33"/>
     </row>
     <row r="40" spans="1:23" ht="21.75" customHeight="1">
       <c r="A40" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="D40" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>190</v>
-      </c>
       <c r="E40" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>42</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I40" s="14">
         <v>3</v>
@@ -9693,25 +9693,25 @@
         <v>39</v>
       </c>
       <c r="B41" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>192</v>
-      </c>
       <c r="D41" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I41" s="17">
         <v>3</v>
@@ -9764,25 +9764,25 @@
         <v>39</v>
       </c>
       <c r="B42" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C42" s="15" t="s">
-        <v>194</v>
-      </c>
       <c r="D42" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>42</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I42" s="14">
         <v>4</v>
@@ -9835,25 +9835,25 @@
         <v>39</v>
       </c>
       <c r="B43" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="C43" s="18" t="s">
-        <v>196</v>
-      </c>
       <c r="D43" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>42</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I43" s="17">
         <v>2</v>
@@ -9902,56 +9902,56 @@
       </c>
     </row>
     <row r="44" spans="1:23" ht="18" customHeight="1">
-      <c r="A44" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="35"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="36"/>
+      <c r="A44" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
+      <c r="T44" s="32"/>
+      <c r="U44" s="32"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="33"/>
     </row>
     <row r="45" spans="1:23" ht="21.75" customHeight="1">
       <c r="A45" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B45" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="D45" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="D45" s="14" t="s">
-        <v>200</v>
-      </c>
       <c r="E45" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G45" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H45" s="16" t="s">
         <v>103</v>
-      </c>
-      <c r="H45" s="16" t="s">
-        <v>104</v>
       </c>
       <c r="I45" s="14">
         <v>2</v>
@@ -10004,25 +10004,25 @@
         <v>26</v>
       </c>
       <c r="B46" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C46" s="18" t="s">
-        <v>202</v>
-      </c>
       <c r="D46" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>29</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I46" s="17">
         <v>3</v>
@@ -10075,25 +10075,25 @@
         <v>26</v>
       </c>
       <c r="B47" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="D47" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I47" s="14">
         <v>6</v>
@@ -10146,25 +10146,25 @@
         <v>26</v>
       </c>
       <c r="B48" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C48" s="18" t="s">
-        <v>206</v>
-      </c>
       <c r="D48" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>29</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I48" s="17">
         <v>4</v>
@@ -10217,25 +10217,25 @@
         <v>26</v>
       </c>
       <c r="B49" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>208</v>
-      </c>
       <c r="D49" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I49" s="14">
         <v>3</v>
@@ -10284,56 +10284,56 @@
       </c>
     </row>
     <row r="50" spans="1:23" ht="18" customHeight="1">
-      <c r="A50" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="B50" s="35"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="35"/>
-      <c r="M50" s="35"/>
-      <c r="N50" s="35"/>
-      <c r="O50" s="35"/>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="35"/>
-      <c r="R50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-      <c r="U50" s="35"/>
-      <c r="V50" s="35"/>
-      <c r="W50" s="36"/>
+      <c r="A50" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="33"/>
     </row>
     <row r="51" spans="1:23" ht="21.75" customHeight="1">
       <c r="A51" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B51" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="D51" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="E51" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>213</v>
-      </c>
       <c r="H51" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I51" s="14">
         <v>3</v>
@@ -10386,25 +10386,25 @@
         <v>10</v>
       </c>
       <c r="B52" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C52" s="18" t="s">
-        <v>215</v>
-      </c>
       <c r="D52" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I52" s="17">
         <v>3</v>
@@ -10457,25 +10457,25 @@
         <v>10</v>
       </c>
       <c r="B53" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C53" s="15" t="s">
-        <v>217</v>
-      </c>
       <c r="D53" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I53" s="14">
         <v>4</v>
@@ -10528,25 +10528,25 @@
         <v>10</v>
       </c>
       <c r="B54" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C54" s="18" t="s">
-        <v>219</v>
-      </c>
       <c r="D54" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I54" s="17">
         <v>3</v>
@@ -10599,25 +10599,25 @@
         <v>10</v>
       </c>
       <c r="B55" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>221</v>
-      </c>
       <c r="D55" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I55" s="14">
         <v>4</v>
@@ -10666,56 +10666,56 @@
       </c>
     </row>
     <row r="56" spans="1:23" ht="18" customHeight="1">
-      <c r="A56" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
-      <c r="J56" s="35"/>
-      <c r="K56" s="35"/>
-      <c r="L56" s="35"/>
-      <c r="M56" s="35"/>
-      <c r="N56" s="35"/>
-      <c r="O56" s="35"/>
-      <c r="P56" s="35"/>
-      <c r="Q56" s="35"/>
-      <c r="R56" s="35"/>
-      <c r="S56" s="35"/>
-      <c r="T56" s="35"/>
-      <c r="U56" s="35"/>
-      <c r="V56" s="35"/>
-      <c r="W56" s="36"/>
+      <c r="A56" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="33"/>
     </row>
     <row r="57" spans="1:23" ht="21.75" customHeight="1">
       <c r="A57" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B57" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="D57" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>225</v>
-      </c>
       <c r="E57" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I57" s="14">
         <v>4</v>
@@ -10768,25 +10768,25 @@
         <v>10</v>
       </c>
       <c r="B58" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C58" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="D58" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G58" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="D58" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>228</v>
-      </c>
       <c r="H58" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I58" s="17">
         <v>3</v>
@@ -10839,25 +10839,25 @@
         <v>10</v>
       </c>
       <c r="B59" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C59" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>230</v>
-      </c>
       <c r="D59" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I59" s="14">
         <v>4</v>
@@ -10910,25 +10910,25 @@
         <v>10</v>
       </c>
       <c r="B60" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="C60" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="C60" s="18" t="s">
-        <v>232</v>
-      </c>
       <c r="D60" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I60" s="17">
         <v>3</v>
@@ -10977,56 +10977,56 @@
       </c>
     </row>
     <row r="61" spans="1:23" ht="18" customHeight="1">
-      <c r="A61" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
-      <c r="M61" s="35"/>
-      <c r="N61" s="35"/>
-      <c r="O61" s="35"/>
-      <c r="P61" s="35"/>
-      <c r="Q61" s="35"/>
-      <c r="R61" s="35"/>
-      <c r="S61" s="35"/>
-      <c r="T61" s="35"/>
-      <c r="U61" s="35"/>
-      <c r="V61" s="35"/>
-      <c r="W61" s="36"/>
+      <c r="A61" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="33"/>
     </row>
     <row r="62" spans="1:23" ht="21.75" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>235</v>
-      </c>
       <c r="D62" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I62" s="14">
         <v>2</v>
@@ -11076,28 +11076,28 @@
     </row>
     <row r="63" spans="1:23" ht="21.75" customHeight="1">
       <c r="A63" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="C63" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="C63" s="18" t="s">
-        <v>237</v>
-      </c>
       <c r="D63" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I63" s="17">
         <v>6</v>
@@ -11147,28 +11147,28 @@
     </row>
     <row r="64" spans="1:23" ht="21.75" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B64" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C64" s="15" t="s">
-        <v>239</v>
-      </c>
       <c r="D64" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I64" s="14">
         <v>4</v>
@@ -11218,28 +11218,28 @@
     </row>
     <row r="65" spans="1:23" ht="21.75" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B65" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C65" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="C65" s="18" t="s">
-        <v>241</v>
-      </c>
       <c r="D65" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I65" s="17">
         <v>3</v>
@@ -11288,56 +11288,56 @@
       </c>
     </row>
     <row r="66" spans="1:23" ht="18" customHeight="1">
-      <c r="A66" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="35"/>
-      <c r="L66" s="35"/>
-      <c r="M66" s="35"/>
-      <c r="N66" s="35"/>
-      <c r="O66" s="35"/>
-      <c r="P66" s="35"/>
-      <c r="Q66" s="35"/>
-      <c r="R66" s="35"/>
-      <c r="S66" s="35"/>
-      <c r="T66" s="35"/>
-      <c r="U66" s="35"/>
-      <c r="V66" s="35"/>
-      <c r="W66" s="36"/>
+      <c r="A66" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
+      <c r="L66" s="32"/>
+      <c r="M66" s="32"/>
+      <c r="N66" s="32"/>
+      <c r="O66" s="32"/>
+      <c r="P66" s="32"/>
+      <c r="Q66" s="32"/>
+      <c r="R66" s="32"/>
+      <c r="S66" s="32"/>
+      <c r="T66" s="32"/>
+      <c r="U66" s="32"/>
+      <c r="V66" s="32"/>
+      <c r="W66" s="33"/>
     </row>
     <row r="67" spans="1:23" ht="21.75" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B67" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C67" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="D67" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D67" s="14" t="s">
-        <v>245</v>
-      </c>
       <c r="E67" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I67" s="14">
         <v>3</v>
@@ -11387,28 +11387,28 @@
     </row>
     <row r="68" spans="1:23" ht="21.75" customHeight="1">
       <c r="A68" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C68" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="C68" s="18" t="s">
-        <v>247</v>
-      </c>
       <c r="D68" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I68" s="17">
         <v>4</v>
@@ -11458,28 +11458,28 @@
     </row>
     <row r="69" spans="1:23" ht="21.75" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B69" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C69" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C69" s="15" t="s">
-        <v>249</v>
-      </c>
       <c r="D69" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I69" s="14">
         <v>3</v>
@@ -11529,28 +11529,28 @@
     </row>
     <row r="70" spans="1:23" ht="21.75" customHeight="1">
       <c r="A70" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C70" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="C70" s="18" t="s">
-        <v>251</v>
-      </c>
       <c r="D70" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F70" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I70" s="17">
         <v>2</v>
@@ -11599,56 +11599,56 @@
       </c>
     </row>
     <row r="71" spans="1:23" ht="18" customHeight="1">
-      <c r="A71" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="B71" s="35"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="35"/>
-      <c r="K71" s="35"/>
-      <c r="L71" s="35"/>
-      <c r="M71" s="35"/>
-      <c r="N71" s="35"/>
-      <c r="O71" s="35"/>
-      <c r="P71" s="35"/>
-      <c r="Q71" s="35"/>
-      <c r="R71" s="35"/>
-      <c r="S71" s="35"/>
-      <c r="T71" s="35"/>
-      <c r="U71" s="35"/>
-      <c r="V71" s="35"/>
-      <c r="W71" s="36"/>
+      <c r="A71" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="32"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="32"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="32"/>
+      <c r="S71" s="32"/>
+      <c r="T71" s="32"/>
+      <c r="U71" s="32"/>
+      <c r="V71" s="32"/>
+      <c r="W71" s="33"/>
     </row>
     <row r="72" spans="1:23" ht="21.75" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B72" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C72" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="D72" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G72" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D72" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G72" s="14" t="s">
-        <v>255</v>
-      </c>
       <c r="H72" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I72" s="14">
         <v>1</v>
@@ -11698,28 +11698,28 @@
     </row>
     <row r="73" spans="1:23" ht="21.75" customHeight="1">
       <c r="A73" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="C73" s="18" t="s">
-        <v>257</v>
-      </c>
       <c r="D73" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I73" s="17">
         <v>3</v>
@@ -11769,28 +11769,28 @@
     </row>
     <row r="74" spans="1:23" ht="21.75" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B74" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C74" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C74" s="15" t="s">
-        <v>259</v>
-      </c>
       <c r="D74" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I74" s="14">
         <v>2</v>
@@ -11839,56 +11839,56 @@
       </c>
     </row>
     <row r="75" spans="1:23" ht="18" customHeight="1">
-      <c r="A75" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
-      <c r="L75" s="35"/>
-      <c r="M75" s="35"/>
-      <c r="N75" s="35"/>
-      <c r="O75" s="35"/>
-      <c r="P75" s="35"/>
-      <c r="Q75" s="35"/>
-      <c r="R75" s="35"/>
-      <c r="S75" s="35"/>
-      <c r="T75" s="35"/>
-      <c r="U75" s="35"/>
-      <c r="V75" s="35"/>
-      <c r="W75" s="36"/>
+      <c r="A75" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
+      <c r="L75" s="32"/>
+      <c r="M75" s="32"/>
+      <c r="N75" s="32"/>
+      <c r="O75" s="32"/>
+      <c r="P75" s="32"/>
+      <c r="Q75" s="32"/>
+      <c r="R75" s="32"/>
+      <c r="S75" s="32"/>
+      <c r="T75" s="32"/>
+      <c r="U75" s="32"/>
+      <c r="V75" s="32"/>
+      <c r="W75" s="33"/>
     </row>
     <row r="76" spans="1:23" ht="21.75" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="C76" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="D76" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="E76" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G76" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="E76" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="F76" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G76" s="14" t="s">
-        <v>264</v>
-      </c>
       <c r="H76" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I76" s="14">
         <v>4</v>
@@ -11938,28 +11938,28 @@
     </row>
     <row r="77" spans="1:23" ht="21.75" customHeight="1">
       <c r="A77" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="C77" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="18" t="s">
-        <v>266</v>
-      </c>
       <c r="D77" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G77" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="E77" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="F77" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G77" s="17" t="s">
-        <v>264</v>
-      </c>
       <c r="H77" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I77" s="17">
         <v>3</v>
@@ -12009,28 +12009,28 @@
     </row>
     <row r="78" spans="1:23" ht="21.75" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B78" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C78" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C78" s="15" t="s">
-        <v>268</v>
-      </c>
       <c r="D78" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G78" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="E78" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="F78" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G78" s="14" t="s">
-        <v>264</v>
-      </c>
       <c r="H78" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I78" s="14">
         <v>4</v>
@@ -12080,28 +12080,28 @@
     </row>
     <row r="79" spans="1:23" ht="21.75" customHeight="1">
       <c r="A79" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B79" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="C79" s="18" t="s">
-        <v>270</v>
-      </c>
       <c r="D79" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G79" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="E79" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="F79" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G79" s="17" t="s">
-        <v>264</v>
-      </c>
       <c r="H79" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I79" s="17">
         <v>5</v>
@@ -12151,28 +12151,28 @@
     </row>
     <row r="80" spans="1:23" ht="21.75" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C80" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C80" s="15" t="s">
-        <v>272</v>
-      </c>
       <c r="D80" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I80" s="14">
         <v>2</v>
@@ -12222,28 +12222,28 @@
     </row>
     <row r="81" spans="1:23" ht="21.75" customHeight="1">
       <c r="A81" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="C81" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="C81" s="18" t="s">
-        <v>274</v>
-      </c>
       <c r="D81" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I81" s="17">
         <v>2</v>
@@ -12292,56 +12292,56 @@
       </c>
     </row>
     <row r="82" spans="1:23" ht="18" customHeight="1">
-      <c r="A82" s="34" t="s">
-        <v>275</v>
-      </c>
-      <c r="B82" s="35"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="35"/>
-      <c r="K82" s="35"/>
-      <c r="L82" s="35"/>
-      <c r="M82" s="35"/>
-      <c r="N82" s="35"/>
-      <c r="O82" s="35"/>
-      <c r="P82" s="35"/>
-      <c r="Q82" s="35"/>
-      <c r="R82" s="35"/>
-      <c r="S82" s="35"/>
-      <c r="T82" s="35"/>
-      <c r="U82" s="35"/>
-      <c r="V82" s="35"/>
-      <c r="W82" s="36"/>
+      <c r="A82" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+      <c r="J82" s="32"/>
+      <c r="K82" s="32"/>
+      <c r="L82" s="32"/>
+      <c r="M82" s="32"/>
+      <c r="N82" s="32"/>
+      <c r="O82" s="32"/>
+      <c r="P82" s="32"/>
+      <c r="Q82" s="32"/>
+      <c r="R82" s="32"/>
+      <c r="S82" s="32"/>
+      <c r="T82" s="32"/>
+      <c r="U82" s="32"/>
+      <c r="V82" s="32"/>
+      <c r="W82" s="33"/>
     </row>
     <row r="83" spans="1:23" ht="21.75" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B83" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C83" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="D83" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D83" s="14" t="s">
-        <v>278</v>
-      </c>
       <c r="E83" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I83" s="14">
         <v>4</v>
@@ -12391,28 +12391,28 @@
     </row>
     <row r="84" spans="1:23" ht="21.75" customHeight="1">
       <c r="A84" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B84" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="C84" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="C84" s="18" t="s">
-        <v>280</v>
-      </c>
       <c r="D84" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F84" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I84" s="17">
         <v>5</v>
@@ -12462,28 +12462,28 @@
     </row>
     <row r="85" spans="1:23" ht="21.75" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B85" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C85" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="C85" s="15" t="s">
-        <v>282</v>
-      </c>
       <c r="D85" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I85" s="14">
         <v>4</v>
@@ -12533,28 +12533,28 @@
     </row>
     <row r="86" spans="1:23" ht="21.75" customHeight="1">
       <c r="A86" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B86" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="C86" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="C86" s="18" t="s">
-        <v>284</v>
-      </c>
       <c r="D86" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F86" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I86" s="17">
         <v>6</v>
@@ -12604,28 +12604,28 @@
     </row>
     <row r="87" spans="1:23" ht="21.75" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B87" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C87" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="15" t="s">
-        <v>286</v>
-      </c>
       <c r="D87" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G87" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I87" s="14">
         <v>3</v>
@@ -13591,6 +13591,11 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A10:W10"/>
+    <mergeCell ref="A15:W15"/>
+    <mergeCell ref="A21:W21"/>
     <mergeCell ref="A27:W27"/>
     <mergeCell ref="A33:W33"/>
     <mergeCell ref="A75:W75"/>
@@ -13602,11 +13607,6 @@
     <mergeCell ref="A61:W61"/>
     <mergeCell ref="A66:W66"/>
     <mergeCell ref="A71:W71"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="A4:W4"/>
-    <mergeCell ref="A10:W10"/>
-    <mergeCell ref="A15:W15"/>
-    <mergeCell ref="A21:W21"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="H5:H9 H11:H14 H16:H20 H22:H26 H28:H32 H34:H38 H40:H43 H45:H49 H51:H55 H57:H60 H62:H65 H67:H70 H72:H74 H76:H81 H83:H88" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -13635,156 +13635,156 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C1" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>289</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>316</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -13812,31 +13812,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="C1" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>334</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -13844,7 +13844,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C2" s="24">
         <v>46297</v>
@@ -13853,19 +13853,19 @@
         <v>46297</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="G2" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="I2" s="26" t="s">
         <v>339</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -13873,28 +13873,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C3" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="E3" s="28" t="s">
+      <c r="F3" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G3" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="H3" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="I3" s="29" t="s">
         <v>345</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -13902,28 +13902,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>350</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -13931,28 +13931,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>352</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>353</v>
-      </c>
       <c r="D5" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E5" s="28" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="H5" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="I5" s="29" t="s">
         <v>356</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -13960,28 +13960,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="D6" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="E6" s="25" t="s">
+      <c r="F6" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="G6" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="I6" s="26" t="s">
         <v>363</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -13989,7 +13989,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C7" s="30">
         <v>46268</v>
@@ -13998,19 +13998,19 @@
         <v>46268</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F7" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>365</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="I7" s="29" t="s">
         <v>367</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -14018,7 +14018,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C8" s="24">
         <v>46329</v>
@@ -14030,16 +14030,16 @@
         <v>42</v>
       </c>
       <c r="F8" s="26" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="H8" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="I8" s="26" t="s">
         <v>372</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -14047,28 +14047,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>375</v>
-      </c>
       <c r="D9" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>29</v>
       </c>
       <c r="F9" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>376</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="H9" s="29" t="s">
         <v>377</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="I9" s="29" t="s">
         <v>378</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14076,28 +14076,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C10" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="26" t="s">
+      <c r="G10" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="H10" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="I10" s="26" t="s">
         <v>383</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -14105,28 +14105,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C11" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="29" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="29" t="s">
+      <c r="G11" s="29" t="s">
         <v>386</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="H11" s="29" t="s">
         <v>387</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="I11" s="29" t="s">
         <v>388</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -14134,28 +14134,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="26" t="s">
+      <c r="G12" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="H12" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="I12" s="26" t="s">
         <v>393</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -14163,28 +14163,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C13" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="29" t="s">
         <v>395</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="29" t="s">
+      <c r="G13" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="H13" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="I13" s="29" t="s">
         <v>398</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -14192,28 +14192,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="26" t="s">
+      <c r="G14" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="H14" s="26" t="s">
         <v>402</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="I14" s="26" t="s">
         <v>403</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -14221,28 +14221,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C15" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="29" t="s">
         <v>405</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>405</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="29" t="s">
+      <c r="G15" s="29" t="s">
         <v>406</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="H15" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="I15" s="29" t="s">
         <v>408</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -14250,28 +14250,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>410</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="26" t="s">
+      <c r="G16" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="H16" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="I16" s="26" t="s">
         <v>414</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="17" spans="5:5">
